--- a/config/testdata/data.xlsx
+++ b/config/testdata/data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khatt003\Desktop\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khatt003\Desktop\Files\Playwright_TS_Cucumber\config\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70E7104-A48E-4546-BD61-2EFA3EFCDF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45063C90-6CC1-4252-8956-C3EEAC17B04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7500" xr2:uid="{91D30866-6A82-43D5-83F1-F5F23CE7AAF4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="9560" activeTab="1" xr2:uid="{91D30866-6A82-43D5-83F1-F5F23CE7AAF4}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
+    <sheet name="ISRData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,12 +40,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>6RFWZWZ3VC4H</t>
   </si>
   <si>
     <t>censusId</t>
+  </si>
+  <si>
+    <t>Select “Yes” if you:Have been staying at the address for more than two monthsIntend to be at the address for more than two months, but have been there less time than that as of the current dateHave no other PERMANENT place to stay AND are living or staying thereAre staying at the address even for a short timeAre away from the address, but do not plan to be away for more than two months</t>
+  </si>
+  <si>
+    <t>HelpTextPage2</t>
   </si>
 </sst>
 </file>
@@ -60,12 +67,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -80,8 +93,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,14 +437,15 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="126.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="214.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -435,4 +453,27 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDF8E6CF-676C-4715-AFCE-46A35C7F7C69}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="85.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>